--- a/diseases/d068/2000-2004.xlsx
+++ b/diseases/d068/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21200,7 +21200,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24764,7 +24764,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25952,7 +25952,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -28328,7 +28328,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29516,7 +29516,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30704,7 +30704,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31892,7 +31892,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -33080,7 +33080,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -34268,7 +34268,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35456,7 +35456,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36644,7 +36644,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37832,7 +37832,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -39020,7 +39020,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -40208,7 +40208,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -41396,7 +41396,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42584,7 +42584,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -43772,7 +43772,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44960,7 +44960,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -45356,7 +45356,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46544,7 +46544,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -46940,7 +46940,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -48128,7 +48128,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -48524,7 +48524,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -49712,7 +49712,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -50108,7 +50108,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -51296,7 +51296,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -51692,7 +51692,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -52880,7 +52880,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -53276,7 +53276,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -54464,7 +54464,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -54860,7 +54860,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -56048,7 +56048,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -56444,7 +56444,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -57632,7 +57632,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -58028,7 +58028,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -59216,7 +59216,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -59612,7 +59612,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -60800,7 +60800,7 @@
       </c>
       <c r="AJ305" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK305" t="inlineStr">
@@ -61196,7 +61196,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -62384,7 +62384,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -62780,7 +62780,7 @@
       </c>
       <c r="AJ315" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK315" t="inlineStr">
@@ -63968,7 +63968,7 @@
       </c>
       <c r="AJ321" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK321" t="inlineStr">
@@ -64364,7 +64364,7 @@
       </c>
       <c r="AJ323" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK323" t="inlineStr">
@@ -65552,7 +65552,7 @@
       </c>
       <c r="AJ329" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK329" t="inlineStr">
@@ -65948,7 +65948,7 @@
       </c>
       <c r="AJ331" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK331" t="inlineStr">
@@ -67136,7 +67136,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -67532,7 +67532,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -68720,7 +68720,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -69116,7 +69116,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -70304,7 +70304,7 @@
       </c>
       <c r="AJ353" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK353" t="inlineStr">
@@ -70700,7 +70700,7 @@
       </c>
       <c r="AJ355" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK355" t="inlineStr">
@@ -71888,7 +71888,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">
@@ -72284,7 +72284,7 @@
       </c>
       <c r="AJ363" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK363" t="inlineStr">
@@ -73472,7 +73472,7 @@
       </c>
       <c r="AJ369" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK369" t="inlineStr">
@@ -73868,7 +73868,7 @@
       </c>
       <c r="AJ371" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK371" t="inlineStr">
@@ -75056,7 +75056,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">
@@ -75452,7 +75452,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -76640,7 +76640,7 @@
       </c>
       <c r="AJ385" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK385" t="inlineStr">
@@ -77036,7 +77036,7 @@
       </c>
       <c r="AJ387" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK387" t="inlineStr">
@@ -78224,7 +78224,7 @@
       </c>
       <c r="AJ393" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK393" t="inlineStr">
@@ -78620,7 +78620,7 @@
       </c>
       <c r="AJ395" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK395" t="inlineStr">
@@ -79808,7 +79808,7 @@
       </c>
       <c r="AJ401" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK401" t="inlineStr">
@@ -80204,7 +80204,7 @@
       </c>
       <c r="AJ403" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK403" t="inlineStr">
@@ -81392,7 +81392,7 @@
       </c>
       <c r="AJ409" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK409" t="inlineStr">

--- a/diseases/d068/2000-2004.xlsx
+++ b/diseases/d068/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21200,7 +21200,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24764,7 +24764,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25952,7 +25952,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -28328,7 +28328,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29516,7 +29516,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30704,7 +30704,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31892,7 +31892,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -33080,7 +33080,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -34268,7 +34268,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35456,7 +35456,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36644,7 +36644,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37832,7 +37832,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -39020,7 +39020,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -40208,7 +40208,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -41396,7 +41396,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42584,7 +42584,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -43772,7 +43772,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44960,7 +44960,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -45356,7 +45356,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46544,7 +46544,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -46940,7 +46940,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -48128,7 +48128,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -48524,7 +48524,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -49712,7 +49712,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -50108,7 +50108,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -51296,7 +51296,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -51692,7 +51692,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -52880,7 +52880,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -53276,7 +53276,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -54464,7 +54464,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -54860,7 +54860,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -56048,7 +56048,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -56444,7 +56444,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -57632,7 +57632,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -58028,7 +58028,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -59216,7 +59216,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -59612,7 +59612,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -60800,7 +60800,7 @@
       </c>
       <c r="AJ305" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK305" t="inlineStr">
@@ -61196,7 +61196,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -62384,7 +62384,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -62780,7 +62780,7 @@
       </c>
       <c r="AJ315" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK315" t="inlineStr">
@@ -63968,7 +63968,7 @@
       </c>
       <c r="AJ321" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK321" t="inlineStr">
@@ -64364,7 +64364,7 @@
       </c>
       <c r="AJ323" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK323" t="inlineStr">
@@ -65552,7 +65552,7 @@
       </c>
       <c r="AJ329" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK329" t="inlineStr">
@@ -65948,7 +65948,7 @@
       </c>
       <c r="AJ331" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK331" t="inlineStr">
@@ -67136,7 +67136,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -67532,7 +67532,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -68720,7 +68720,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -69116,7 +69116,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -70304,7 +70304,7 @@
       </c>
       <c r="AJ353" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK353" t="inlineStr">
@@ -70700,7 +70700,7 @@
       </c>
       <c r="AJ355" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK355" t="inlineStr">
@@ -71888,7 +71888,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">
@@ -72284,7 +72284,7 @@
       </c>
       <c r="AJ363" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK363" t="inlineStr">
@@ -73472,7 +73472,7 @@
       </c>
       <c r="AJ369" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK369" t="inlineStr">
@@ -73868,7 +73868,7 @@
       </c>
       <c r="AJ371" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK371" t="inlineStr">
@@ -75056,7 +75056,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">
@@ -75452,7 +75452,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -76640,7 +76640,7 @@
       </c>
       <c r="AJ385" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK385" t="inlineStr">
@@ -77036,7 +77036,7 @@
       </c>
       <c r="AJ387" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK387" t="inlineStr">
@@ -78224,7 +78224,7 @@
       </c>
       <c r="AJ393" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK393" t="inlineStr">
@@ -78620,7 +78620,7 @@
       </c>
       <c r="AJ395" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK395" t="inlineStr">
@@ -79808,7 +79808,7 @@
       </c>
       <c r="AJ401" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK401" t="inlineStr">
@@ -80204,7 +80204,7 @@
       </c>
       <c r="AJ403" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK403" t="inlineStr">
@@ -81392,7 +81392,7 @@
       </c>
       <c r="AJ409" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK409" t="inlineStr">

--- a/diseases/d068/2000-2004.xlsx
+++ b/diseases/d068/2000-2004.xlsx
@@ -1161,9 +1161,6 @@
       <c r="O4" t="n">
         <v>2</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.03863837217310803</v>
       </c>
@@ -1557,9 +1554,6 @@
       <c r="O6" t="n">
         <v>8</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.1781393214272433</v>
       </c>
@@ -2349,9 +2343,6 @@
       <c r="O10" t="n">
         <v>9</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.1738726747789861</v>
       </c>
@@ -2745,9 +2736,6 @@
       <c r="O12" t="n">
         <v>23</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.5121505491033246</v>
       </c>
@@ -3537,9 +3525,6 @@
       <c r="O16" t="n">
         <v>4</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.07727674434621605</v>
       </c>
@@ -3933,9 +3918,6 @@
       <c r="O18" t="n">
         <v>26</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.5789527946385408</v>
       </c>
@@ -4725,9 +4707,6 @@
       <c r="O22" t="n">
         <v>14</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.2704686052117561</v>
       </c>
@@ -5121,9 +5100,6 @@
       <c r="O24" t="n">
         <v>27</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.6012202098169462</v>
       </c>
@@ -5913,9 +5889,6 @@
       <c r="O28" t="n">
         <v>14</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.2704686052117561</v>
       </c>
@@ -6309,9 +6282,6 @@
       <c r="O30" t="n">
         <v>23</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.5121505491033246</v>
       </c>
@@ -7101,9 +7071,6 @@
       <c r="O34" t="n">
         <v>16</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.3091069773848642</v>
       </c>
@@ -7497,9 +7464,6 @@
       <c r="O36" t="n">
         <v>12</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.267208982140865</v>
       </c>
@@ -8289,9 +8253,6 @@
       <c r="O40" t="n">
         <v>10</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.1931918608655401</v>
       </c>
@@ -8685,9 +8646,6 @@
       <c r="O42" t="n">
         <v>21</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.4676157187465137</v>
       </c>
@@ -9477,9 +9435,6 @@
       <c r="O46" t="n">
         <v>10</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.1931918608655401</v>
       </c>
@@ -9873,9 +9828,6 @@
       <c r="O48" t="n">
         <v>24</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.5344179642817301</v>
       </c>
@@ -10665,9 +10617,6 @@
       <c r="O52" t="n">
         <v>8</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.1545534886924321</v>
       </c>
@@ -11061,9 +11010,6 @@
       <c r="O54" t="n">
         <v>34</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.7570921160657842</v>
       </c>
@@ -11853,9 +11799,6 @@
       <c r="O58" t="n">
         <v>4</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.07727674434621605</v>
       </c>
@@ -12249,9 +12192,6 @@
       <c r="O60" t="n">
         <v>20</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.4453483035681083</v>
       </c>
@@ -13041,9 +12981,6 @@
       <c r="O64" t="n">
         <v>3</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.05795755825966203</v>
       </c>
@@ -13437,9 +13374,6 @@
       <c r="O66" t="n">
         <v>23</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.5121505491033246</v>
       </c>
@@ -14229,9 +14163,6 @@
       <c r="O70" t="n">
         <v>6</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.1159151165193241</v>
       </c>
@@ -14625,9 +14556,6 @@
       <c r="O72" t="n">
         <v>21</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.4676157187465137</v>
       </c>
@@ -15417,9 +15345,6 @@
       <c r="O76" t="n">
         <v>4</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.07710143329636962</v>
       </c>
@@ -15813,9 +15738,6 @@
       <c r="O78" t="n">
         <v>13</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.2880147959847193</v>
       </c>
@@ -16605,9 +16527,6 @@
       <c r="O82" t="n">
         <v>8</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.1542028665927392</v>
       </c>
@@ -17001,9 +16920,6 @@
       <c r="O84" t="n">
         <v>14</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.3101697802912362</v>
       </c>
@@ -17793,9 +17709,6 @@
       <c r="O88" t="n">
         <v>8</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.1542028665927392</v>
       </c>
@@ -18189,9 +18102,6 @@
       <c r="O90" t="n">
         <v>26</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.5760295919694386</v>
       </c>
@@ -18981,9 +18891,6 @@
       <c r="O94" t="n">
         <v>2</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.03855071664818481</v>
       </c>
@@ -19377,9 +19284,6 @@
       <c r="O96" t="n">
         <v>18</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.3987897175173036</v>
       </c>
@@ -20169,9 +20073,6 @@
       <c r="O100" t="n">
         <v>1</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -20565,9 +20466,6 @@
       <c r="O102" t="n">
         <v>28</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.6203395605824723</v>
       </c>
@@ -21357,9 +21255,6 @@
       <c r="O106" t="n">
         <v>3</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.05782607497227721</v>
       </c>
@@ -21753,9 +21648,6 @@
       <c r="O108" t="n">
         <v>11</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.2437048273716855</v>
       </c>
@@ -22545,9 +22437,6 @@
       <c r="O112" t="n">
         <v>7</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.1349275082686468</v>
       </c>
@@ -22941,9 +22830,6 @@
       <c r="O114" t="n">
         <v>17</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.3766347332107867</v>
       </c>
@@ -23733,9 +23619,6 @@
       <c r="O118" t="n">
         <v>5</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.09637679162046203</v>
       </c>
@@ -24129,9 +24012,6 @@
       <c r="O120" t="n">
         <v>15</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.332324764597753</v>
       </c>
@@ -24921,9 +24801,6 @@
       <c r="O124" t="n">
         <v>6</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.1156521499445544</v>
       </c>
@@ -25317,9 +25194,6 @@
       <c r="O126" t="n">
         <v>18</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.3987897175173036</v>
       </c>
@@ -26109,9 +25983,6 @@
       <c r="O130" t="n">
         <v>9</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.1734782249168317</v>
       </c>
@@ -26505,9 +26376,6 @@
       <c r="O132" t="n">
         <v>6</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.1329299058391012</v>
       </c>
@@ -27297,9 +27165,6 @@
       <c r="O136" t="n">
         <v>11</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.2120289415650165</v>
       </c>
@@ -27693,9 +27558,6 @@
       <c r="O138" t="n">
         <v>11</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.2437048273716855</v>
       </c>
@@ -28485,9 +28347,6 @@
       <c r="O142" t="n">
         <v>4</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.07710143329636962</v>
       </c>
@@ -28881,9 +28740,6 @@
       <c r="O144" t="n">
         <v>24</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.5317196233564048</v>
       </c>
@@ -29673,9 +29529,6 @@
       <c r="O148" t="n">
         <v>8</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.1538300016959758</v>
       </c>
@@ -30069,9 +29922,6 @@
       <c r="O150" t="n">
         <v>9</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.1983246415722825</v>
       </c>
@@ -30861,9 +30711,6 @@
       <c r="O154" t="n">
         <v>8</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.1538300016959758</v>
       </c>
@@ -31257,9 +31104,6 @@
       <c r="O156" t="n">
         <v>8</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.1762885702864733</v>
       </c>
@@ -32049,9 +31893,6 @@
       <c r="O160" t="n">
         <v>7</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.1346012514839788</v>
       </c>
@@ -32445,9 +32286,6 @@
       <c r="O162" t="n">
         <v>10</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0.2203607128580917</v>
       </c>
@@ -33237,9 +33075,6 @@
       <c r="O166" t="n">
         <v>14</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0.2692025029679576</v>
       </c>
@@ -33633,9 +33468,6 @@
       <c r="O168" t="n">
         <v>13</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.2864689267155192</v>
       </c>
@@ -34425,9 +34257,6 @@
       <c r="O172" t="n">
         <v>15</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0.2884312531799545</v>
       </c>
@@ -34821,9 +34650,6 @@
       <c r="O174" t="n">
         <v>15</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0.3305410692871375</v>
       </c>
@@ -35613,9 +35439,6 @@
       <c r="O178" t="n">
         <v>15</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0.2884312531799545</v>
       </c>
@@ -36009,9 +35832,6 @@
       <c r="O180" t="n">
         <v>16</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0.3525771405729466</v>
       </c>
@@ -36801,9 +36621,6 @@
       <c r="O184" t="n">
         <v>12</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0.2307450025439637</v>
       </c>
@@ -37197,9 +37014,6 @@
       <c r="O186" t="n">
         <v>17</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.3746132118587558</v>
       </c>
@@ -37989,9 +37803,6 @@
       <c r="O190" t="n">
         <v>5</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.09614375105998485</v>
       </c>
@@ -38385,9 +38196,6 @@
       <c r="O192" t="n">
         <v>21</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0.4627574970019925</v>
       </c>
@@ -39177,9 +38985,6 @@
       <c r="O196" t="n">
         <v>12</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0.2307450025439637</v>
       </c>
@@ -39573,9 +39378,6 @@
       <c r="O198" t="n">
         <v>18</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0.396649283144565</v>
       </c>
@@ -40365,9 +40167,6 @@
       <c r="O202" t="n">
         <v>9</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>0.1730587519079727</v>
       </c>
@@ -40761,9 +40560,6 @@
       <c r="O204" t="n">
         <v>20</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0.4407214257161833</v>
       </c>
@@ -41553,9 +41349,6 @@
       <c r="O208" t="n">
         <v>11</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0.2115162523319667</v>
       </c>
@@ -41949,9 +41742,6 @@
       <c r="O210" t="n">
         <v>19</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0.4186853544303741</v>
       </c>
@@ -42741,9 +42531,6 @@
       <c r="O214" t="n">
         <v>3</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0.05768625063599091</v>
       </c>
@@ -43137,9 +42924,6 @@
       <c r="O216" t="n">
         <v>17</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0.3746132118587558</v>
       </c>
@@ -43929,9 +43713,6 @@
       <c r="O220" t="n">
         <v>6</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0.1150978667569545</v>
       </c>
@@ -44325,9 +44106,6 @@
       <c r="O222" t="n">
         <v>12</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0.2628887220519165</v>
       </c>
@@ -44970,7 +44748,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -45513,9 +45291,6 @@
       <c r="O228" t="n">
         <v>13</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0.2493787113067349</v>
       </c>
@@ -45909,9 +45684,6 @@
       <c r="O230" t="n">
         <v>20</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0.4381478700865276</v>
       </c>
@@ -46554,7 +46326,7 @@
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN233" t="b">
@@ -47097,9 +46869,6 @@
       <c r="O236" t="n">
         <v>13</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0.2493787113067349</v>
       </c>
@@ -47493,9 +47262,6 @@
       <c r="O238" t="n">
         <v>12</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0.2628887220519165</v>
       </c>
@@ -48138,7 +47904,7 @@
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN241" t="b">
@@ -48681,9 +48447,6 @@
       <c r="O244" t="n">
         <v>8</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>0.1534638223426061</v>
       </c>
@@ -49077,9 +48840,6 @@
       <c r="O246" t="n">
         <v>17</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>0.3724256895735485</v>
       </c>
@@ -49722,7 +49482,7 @@
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN249" t="b">
@@ -50265,9 +50025,6 @@
       <c r="O252" t="n">
         <v>4</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>0.07673191117130304</v>
       </c>
@@ -50661,9 +50418,6 @@
       <c r="O254" t="n">
         <v>22</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="R254" t="n">
         <v>0.4819626570951804</v>
       </c>
@@ -51306,7 +51060,7 @@
       </c>
       <c r="AM257" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN257" t="b">
@@ -51849,9 +51603,6 @@
       <c r="O260" t="n">
         <v>6</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>0.1150978667569545</v>
       </c>
@@ -52245,9 +51996,6 @@
       <c r="O262" t="n">
         <v>11</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0.2409813285475902</v>
       </c>
@@ -52890,7 +52638,7 @@
       </c>
       <c r="AM265" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN265" t="b">
@@ -53433,9 +53181,6 @@
       <c r="O268" t="n">
         <v>5</v>
       </c>
-      <c r="Q268" t="n">
-        <v>0</v>
-      </c>
       <c r="R268" t="n">
         <v>0.09591488896412878</v>
       </c>
@@ -53829,9 +53574,6 @@
       <c r="O270" t="n">
         <v>9</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>0.1971665415389375</v>
       </c>
@@ -54474,7 +54216,7 @@
       </c>
       <c r="AM273" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN273" t="b">
@@ -55017,9 +54759,6 @@
       <c r="O276" t="n">
         <v>3</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="R276" t="n">
         <v>0.05754893337847727</v>
       </c>
@@ -55413,9 +55152,6 @@
       <c r="O278" t="n">
         <v>21</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0.460055263590854</v>
       </c>
@@ -56058,7 +55794,7 @@
       </c>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN281" t="b">
@@ -56601,9 +56337,6 @@
       <c r="O284" t="n">
         <v>6</v>
       </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
       <c r="R284" t="n">
         <v>0.1150978667569545</v>
       </c>
@@ -56997,9 +56730,6 @@
       <c r="O286" t="n">
         <v>22</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="R286" t="n">
         <v>0.4819626570951804</v>
       </c>
@@ -57642,7 +57372,7 @@
       </c>
       <c r="AM289" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN289" t="b">
@@ -58185,9 +57915,6 @@
       <c r="O292" t="n">
         <v>5</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>0.09591488896412878</v>
       </c>
@@ -58581,9 +58308,6 @@
       <c r="O294" t="n">
         <v>24</v>
       </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
       <c r="R294" t="n">
         <v>0.5257774441038331</v>
       </c>
@@ -59226,7 +58950,7 @@
       </c>
       <c r="AM297" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN297" t="b">
@@ -59769,9 +59493,6 @@
       <c r="O300" t="n">
         <v>3</v>
       </c>
-      <c r="Q300" t="n">
-        <v>0</v>
-      </c>
       <c r="R300" t="n">
         <v>0.05754893337847727</v>
       </c>
@@ -60165,9 +59886,6 @@
       <c r="O302" t="n">
         <v>18</v>
       </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
       <c r="R302" t="n">
         <v>0.3943330830778749</v>
       </c>
@@ -60810,7 +60528,7 @@
       </c>
       <c r="AM305" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN305" t="b">
@@ -61353,9 +61071,6 @@
       <c r="O308" t="n">
         <v>5</v>
       </c>
-      <c r="Q308" t="n">
-        <v>0</v>
-      </c>
       <c r="R308" t="n">
         <v>0.09591488896412878</v>
       </c>
@@ -61749,9 +61464,6 @@
       <c r="O310" t="n">
         <v>16</v>
       </c>
-      <c r="Q310" t="n">
-        <v>0</v>
-      </c>
       <c r="R310" t="n">
         <v>0.3505182960692221</v>
       </c>
@@ -62394,7 +62106,7 @@
       </c>
       <c r="AM313" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN313" t="b">
@@ -62937,9 +62649,6 @@
       <c r="O316" t="n">
         <v>0</v>
       </c>
-      <c r="Q316" t="n">
-        <v>0</v>
-      </c>
       <c r="R316" t="n">
         <v>0</v>
       </c>
@@ -63333,9 +63042,6 @@
       <c r="O318" t="n">
         <v>5</v>
       </c>
-      <c r="Q318" t="n">
-        <v>0</v>
-      </c>
       <c r="R318" t="n">
         <v>0.108891123576725</v>
       </c>
@@ -63978,7 +63684,7 @@
       </c>
       <c r="AM321" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN321" t="b">
@@ -64521,9 +64227,6 @@
       <c r="O324" t="n">
         <v>0</v>
       </c>
-      <c r="Q324" t="n">
-        <v>0</v>
-      </c>
       <c r="R324" t="n">
         <v>0</v>
       </c>
@@ -64917,9 +64620,6 @@
       <c r="O326" t="n">
         <v>9</v>
       </c>
-      <c r="Q326" t="n">
-        <v>0</v>
-      </c>
       <c r="R326" t="n">
         <v>0.1960040224381049</v>
       </c>
@@ -65562,7 +65262,7 @@
       </c>
       <c r="AM329" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN329" t="b">
@@ -66105,9 +65805,6 @@
       <c r="O332" t="n">
         <v>2</v>
       </c>
-      <c r="Q332" t="n">
-        <v>0</v>
-      </c>
       <c r="R332" t="n">
         <v>0.0382544641046887</v>
       </c>
@@ -66501,9 +66198,6 @@
       <c r="O334" t="n">
         <v>23</v>
       </c>
-      <c r="Q334" t="n">
-        <v>0</v>
-      </c>
       <c r="R334" t="n">
         <v>0.5008991684529348</v>
       </c>
@@ -67146,7 +66840,7 @@
       </c>
       <c r="AM337" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN337" t="b">
@@ -67689,9 +67383,6 @@
       <c r="O340" t="n">
         <v>2</v>
       </c>
-      <c r="Q340" t="n">
-        <v>0</v>
-      </c>
       <c r="R340" t="n">
         <v>0.0382544641046887</v>
       </c>
@@ -68085,9 +67776,6 @@
       <c r="O342" t="n">
         <v>11</v>
       </c>
-      <c r="Q342" t="n">
-        <v>0</v>
-      </c>
       <c r="R342" t="n">
         <v>0.2395604718687949</v>
       </c>
@@ -68730,7 +68418,7 @@
       </c>
       <c r="AM345" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN345" t="b">
@@ -69273,9 +68961,6 @@
       <c r="O348" t="n">
         <v>1</v>
       </c>
-      <c r="Q348" t="n">
-        <v>0</v>
-      </c>
       <c r="R348" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -69669,9 +69354,6 @@
       <c r="O350" t="n">
         <v>19</v>
       </c>
-      <c r="Q350" t="n">
-        <v>0</v>
-      </c>
       <c r="R350" t="n">
         <v>0.4137862695915548</v>
       </c>
@@ -70314,7 +69996,7 @@
       </c>
       <c r="AM353" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN353" t="b">
@@ -70857,9 +70539,6 @@
       <c r="O356" t="n">
         <v>4</v>
       </c>
-      <c r="Q356" t="n">
-        <v>0</v>
-      </c>
       <c r="R356" t="n">
         <v>0.07650892820937739</v>
       </c>
@@ -71253,9 +70932,6 @@
       <c r="O358" t="n">
         <v>11</v>
       </c>
-      <c r="Q358" t="n">
-        <v>0</v>
-      </c>
       <c r="R358" t="n">
         <v>0.2395604718687949</v>
       </c>
@@ -71898,7 +71574,7 @@
       </c>
       <c r="AM361" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN361" t="b">
@@ -72441,9 +72117,6 @@
       <c r="O364" t="n">
         <v>3</v>
       </c>
-      <c r="Q364" t="n">
-        <v>0</v>
-      </c>
       <c r="R364" t="n">
         <v>0.05738169615703305</v>
       </c>
@@ -72837,9 +72510,6 @@
       <c r="O366" t="n">
         <v>21</v>
       </c>
-      <c r="Q366" t="n">
-        <v>0</v>
-      </c>
       <c r="R366" t="n">
         <v>0.4573427190222448</v>
       </c>
@@ -73482,7 +73152,7 @@
       </c>
       <c r="AM369" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN369" t="b">
@@ -74025,9 +73695,6 @@
       <c r="O372" t="n">
         <v>4</v>
       </c>
-      <c r="Q372" t="n">
-        <v>0</v>
-      </c>
       <c r="R372" t="n">
         <v>0.07650892820937739</v>
       </c>
@@ -74421,9 +74088,6 @@
       <c r="O374" t="n">
         <v>20</v>
       </c>
-      <c r="Q374" t="n">
-        <v>0</v>
-      </c>
       <c r="R374" t="n">
         <v>0.4355644943068998</v>
       </c>
@@ -75066,7 +74730,7 @@
       </c>
       <c r="AM377" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN377" t="b">
@@ -75609,9 +75273,6 @@
       <c r="O380" t="n">
         <v>2</v>
       </c>
-      <c r="Q380" t="n">
-        <v>0</v>
-      </c>
       <c r="R380" t="n">
         <v>0.0382544641046887</v>
       </c>
@@ -76005,9 +75666,6 @@
       <c r="O382" t="n">
         <v>16</v>
       </c>
-      <c r="Q382" t="n">
-        <v>0</v>
-      </c>
       <c r="R382" t="n">
         <v>0.3484515954455199</v>
       </c>
@@ -76650,7 +76308,7 @@
       </c>
       <c r="AM385" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN385" t="b">
@@ -77193,9 +76851,6 @@
       <c r="O388" t="n">
         <v>2</v>
       </c>
-      <c r="Q388" t="n">
-        <v>0</v>
-      </c>
       <c r="R388" t="n">
         <v>0.0382544641046887</v>
       </c>
@@ -77589,9 +77244,6 @@
       <c r="O390" t="n">
         <v>18</v>
       </c>
-      <c r="Q390" t="n">
-        <v>0</v>
-      </c>
       <c r="R390" t="n">
         <v>0.3920080448762099</v>
       </c>
@@ -78234,7 +77886,7 @@
       </c>
       <c r="AM393" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN393" t="b">
@@ -78777,9 +78429,6 @@
       <c r="O396" t="n">
         <v>3</v>
       </c>
-      <c r="Q396" t="n">
-        <v>0</v>
-      </c>
       <c r="R396" t="n">
         <v>0.05738169615703305</v>
       </c>
@@ -79173,9 +78822,6 @@
       <c r="O398" t="n">
         <v>13</v>
       </c>
-      <c r="Q398" t="n">
-        <v>0</v>
-      </c>
       <c r="R398" t="n">
         <v>0.2831169212994849</v>
       </c>
@@ -79818,7 +79464,7 @@
       </c>
       <c r="AM401" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN401" t="b">
@@ -80361,9 +80007,6 @@
       <c r="O404" t="n">
         <v>2</v>
       </c>
-      <c r="Q404" t="n">
-        <v>0</v>
-      </c>
       <c r="R404" t="n">
         <v>0.0382544641046887</v>
       </c>
@@ -80757,9 +80400,6 @@
       <c r="O406" t="n">
         <v>22</v>
       </c>
-      <c r="Q406" t="n">
-        <v>0</v>
-      </c>
       <c r="R406" t="n">
         <v>0.4791209437375898</v>
       </c>
@@ -81402,7 +81042,7 @@
       </c>
       <c r="AM409" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN409" t="b">

--- a/diseases/d068/2000-2004.xlsx
+++ b/diseases/d068/2000-2004.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -10470,7 +10470,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12834,7 +12834,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -14016,7 +14016,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -15198,7 +15198,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -16380,7 +16380,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -17562,7 +17562,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18744,7 +18744,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19926,7 +19926,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -21108,7 +21108,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -22290,7 +22290,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -23472,7 +23472,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25836,7 +25836,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -27018,7 +27018,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -28200,7 +28200,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -29382,7 +29382,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -30564,7 +30564,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -31746,7 +31746,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -32928,7 +32928,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -34110,7 +34110,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -35292,7 +35292,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -36474,7 +36474,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -37656,7 +37656,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -38838,7 +38838,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -40020,7 +40020,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -41202,7 +41202,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -42384,7 +42384,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -43566,7 +43566,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -45144,7 +45144,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -46722,7 +46722,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -48300,7 +48300,7 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -49878,7 +49878,7 @@
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -51456,7 +51456,7 @@
       </c>
       <c r="AM259" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN259" t="b">
@@ -53034,7 +53034,7 @@
       </c>
       <c r="AM267" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN267" t="b">
@@ -54612,7 +54612,7 @@
       </c>
       <c r="AM275" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN275" t="b">
@@ -56190,7 +56190,7 @@
       </c>
       <c r="AM283" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN283" t="b">
@@ -57768,7 +57768,7 @@
       </c>
       <c r="AM291" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN291" t="b">
@@ -59346,7 +59346,7 @@
       </c>
       <c r="AM299" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN299" t="b">
@@ -60924,7 +60924,7 @@
       </c>
       <c r="AM307" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN307" t="b">
@@ -62502,7 +62502,7 @@
       </c>
       <c r="AM315" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN315" t="b">
@@ -64080,7 +64080,7 @@
       </c>
       <c r="AM323" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN323" t="b">
@@ -65658,7 +65658,7 @@
       </c>
       <c r="AM331" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN331" t="b">
@@ -67236,7 +67236,7 @@
       </c>
       <c r="AM339" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN339" t="b">
@@ -68814,7 +68814,7 @@
       </c>
       <c r="AM347" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN347" t="b">
@@ -70392,7 +70392,7 @@
       </c>
       <c r="AM355" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN355" t="b">
@@ -71970,7 +71970,7 @@
       </c>
       <c r="AM363" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN363" t="b">
@@ -73548,7 +73548,7 @@
       </c>
       <c r="AM371" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN371" t="b">
@@ -75126,7 +75126,7 @@
       </c>
       <c r="AM379" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN379" t="b">
@@ -76704,7 +76704,7 @@
       </c>
       <c r="AM387" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN387" t="b">
@@ -78282,7 +78282,7 @@
       </c>
       <c r="AM395" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN395" t="b">
@@ -79860,7 +79860,7 @@
       </c>
       <c r="AM403" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN403" t="b">

--- a/diseases/d068/2000-2004.xlsx
+++ b/diseases/d068/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10460,7 +10460,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11642,7 +11642,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14006,7 +14006,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15188,7 +15188,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16370,7 +16370,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17552,7 +17552,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18734,7 +18734,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19916,7 +19916,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21098,7 +21098,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22280,7 +22280,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23462,7 +23462,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24644,7 +24644,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25826,7 +25826,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27008,7 +27008,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -28190,7 +28190,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29372,7 +29372,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31736,7 +31736,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32918,7 +32918,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -34100,7 +34100,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35282,7 +35282,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36464,7 +36464,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37646,7 +37646,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -38828,7 +38828,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -40010,7 +40010,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -41192,7 +41192,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42374,7 +42374,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -43556,7 +43556,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44738,7 +44738,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -45134,7 +45134,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46316,7 +46316,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -46712,7 +46712,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -47894,7 +47894,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -48290,7 +48290,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -49472,7 +49472,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -49868,7 +49868,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -51050,7 +51050,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -51446,7 +51446,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -52628,7 +52628,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -53024,7 +53024,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -54206,7 +54206,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -54602,7 +54602,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -55784,7 +55784,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -56180,7 +56180,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -57362,7 +57362,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -57758,7 +57758,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -58940,7 +58940,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -59336,7 +59336,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -60518,7 +60518,7 @@
       </c>
       <c r="AJ305" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK305" t="inlineStr">
@@ -60914,7 +60914,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -62096,7 +62096,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -62492,7 +62492,7 @@
       </c>
       <c r="AJ315" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK315" t="inlineStr">
@@ -63674,7 +63674,7 @@
       </c>
       <c r="AJ321" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK321" t="inlineStr">
@@ -64070,7 +64070,7 @@
       </c>
       <c r="AJ323" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK323" t="inlineStr">
@@ -65252,7 +65252,7 @@
       </c>
       <c r="AJ329" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK329" t="inlineStr">
@@ -65648,7 +65648,7 @@
       </c>
       <c r="AJ331" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK331" t="inlineStr">
@@ -66830,7 +66830,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -67226,7 +67226,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -68408,7 +68408,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -68804,7 +68804,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -69986,7 +69986,7 @@
       </c>
       <c r="AJ353" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK353" t="inlineStr">
@@ -70382,7 +70382,7 @@
       </c>
       <c r="AJ355" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK355" t="inlineStr">
@@ -71564,7 +71564,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">
@@ -71960,7 +71960,7 @@
       </c>
       <c r="AJ363" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK363" t="inlineStr">
@@ -73142,7 +73142,7 @@
       </c>
       <c r="AJ369" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK369" t="inlineStr">
@@ -73538,7 +73538,7 @@
       </c>
       <c r="AJ371" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK371" t="inlineStr">
@@ -74720,7 +74720,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">
@@ -75116,7 +75116,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -76298,7 +76298,7 @@
       </c>
       <c r="AJ385" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK385" t="inlineStr">
@@ -76694,7 +76694,7 @@
       </c>
       <c r="AJ387" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK387" t="inlineStr">
@@ -77876,7 +77876,7 @@
       </c>
       <c r="AJ393" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK393" t="inlineStr">
@@ -78272,7 +78272,7 @@
       </c>
       <c r="AJ395" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK395" t="inlineStr">
@@ -79454,7 +79454,7 @@
       </c>
       <c r="AJ401" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK401" t="inlineStr">
@@ -79850,7 +79850,7 @@
       </c>
       <c r="AJ403" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK403" t="inlineStr">
@@ -81032,7 +81032,7 @@
       </c>
       <c r="AJ409" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK409" t="inlineStr">

--- a/diseases/d068/2000-2004.xlsx
+++ b/diseases/d068/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10460,7 +10460,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11642,7 +11642,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14006,7 +14006,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15188,7 +15188,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16370,7 +16370,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17552,7 +17552,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18734,7 +18734,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19916,7 +19916,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21098,7 +21098,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22280,7 +22280,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23462,7 +23462,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24644,7 +24644,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25826,7 +25826,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27008,7 +27008,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -28190,7 +28190,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29372,7 +29372,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31736,7 +31736,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32918,7 +32918,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -34100,7 +34100,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35282,7 +35282,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36464,7 +36464,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37646,7 +37646,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -38828,7 +38828,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -40010,7 +40010,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -41192,7 +41192,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42374,7 +42374,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -43556,7 +43556,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44738,7 +44738,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -45134,7 +45134,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46316,7 +46316,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -46712,7 +46712,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -47894,7 +47894,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -48290,7 +48290,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -49472,7 +49472,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -49868,7 +49868,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -51050,7 +51050,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -51446,7 +51446,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -52628,7 +52628,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -53024,7 +53024,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -54206,7 +54206,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -54602,7 +54602,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -55784,7 +55784,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -56180,7 +56180,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -57362,7 +57362,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -57758,7 +57758,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -58940,7 +58940,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -59336,7 +59336,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -60518,7 +60518,7 @@
       </c>
       <c r="AJ305" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK305" t="inlineStr">
@@ -60914,7 +60914,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -62096,7 +62096,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -62492,7 +62492,7 @@
       </c>
       <c r="AJ315" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK315" t="inlineStr">
@@ -63674,7 +63674,7 @@
       </c>
       <c r="AJ321" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK321" t="inlineStr">
@@ -64070,7 +64070,7 @@
       </c>
       <c r="AJ323" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK323" t="inlineStr">
@@ -65252,7 +65252,7 @@
       </c>
       <c r="AJ329" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK329" t="inlineStr">
@@ -65648,7 +65648,7 @@
       </c>
       <c r="AJ331" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK331" t="inlineStr">
@@ -66830,7 +66830,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -67226,7 +67226,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -68408,7 +68408,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -68804,7 +68804,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -69986,7 +69986,7 @@
       </c>
       <c r="AJ353" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK353" t="inlineStr">
@@ -70382,7 +70382,7 @@
       </c>
       <c r="AJ355" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK355" t="inlineStr">
@@ -71564,7 +71564,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">
@@ -71960,7 +71960,7 @@
       </c>
       <c r="AJ363" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK363" t="inlineStr">
@@ -73142,7 +73142,7 @@
       </c>
       <c r="AJ369" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK369" t="inlineStr">
@@ -73538,7 +73538,7 @@
       </c>
       <c r="AJ371" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK371" t="inlineStr">
@@ -74720,7 +74720,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">
@@ -75116,7 +75116,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -76298,7 +76298,7 @@
       </c>
       <c r="AJ385" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK385" t="inlineStr">
@@ -76694,7 +76694,7 @@
       </c>
       <c r="AJ387" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK387" t="inlineStr">
@@ -77876,7 +77876,7 @@
       </c>
       <c r="AJ393" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK393" t="inlineStr">
@@ -78272,7 +78272,7 @@
       </c>
       <c r="AJ395" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK395" t="inlineStr">
@@ -79454,7 +79454,7 @@
       </c>
       <c r="AJ401" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK401" t="inlineStr">
@@ -79850,7 +79850,7 @@
       </c>
       <c r="AJ403" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK403" t="inlineStr">
@@ -81032,7 +81032,7 @@
       </c>
       <c r="AJ409" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK409" t="inlineStr">

--- a/diseases/d068/2000-2004.xlsx
+++ b/diseases/d068/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10460,7 +10460,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11642,7 +11642,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14006,7 +14006,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15188,7 +15188,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16370,7 +16370,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17552,7 +17552,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18734,7 +18734,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19916,7 +19916,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21098,7 +21098,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22280,7 +22280,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23462,7 +23462,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24644,7 +24644,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25826,7 +25826,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27008,7 +27008,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -28190,7 +28190,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29372,7 +29372,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31736,7 +31736,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32918,7 +32918,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -34100,7 +34100,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35282,7 +35282,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36464,7 +36464,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37646,7 +37646,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -38828,7 +38828,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -40010,7 +40010,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -41192,7 +41192,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42374,7 +42374,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -43556,7 +43556,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44738,7 +44738,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -45134,7 +45134,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46316,7 +46316,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -46712,7 +46712,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -47894,7 +47894,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -48290,7 +48290,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -49472,7 +49472,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -49868,7 +49868,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -51050,7 +51050,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -51446,7 +51446,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -52628,7 +52628,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -53024,7 +53024,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -54206,7 +54206,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -54602,7 +54602,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -55784,7 +55784,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -56180,7 +56180,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -57362,7 +57362,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -57758,7 +57758,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -58940,7 +58940,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -59336,7 +59336,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -60518,7 +60518,7 @@
       </c>
       <c r="AJ305" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK305" t="inlineStr">
@@ -60914,7 +60914,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -62096,7 +62096,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -62492,7 +62492,7 @@
       </c>
       <c r="AJ315" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK315" t="inlineStr">
@@ -63674,7 +63674,7 @@
       </c>
       <c r="AJ321" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK321" t="inlineStr">
@@ -64070,7 +64070,7 @@
       </c>
       <c r="AJ323" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK323" t="inlineStr">
@@ -65252,7 +65252,7 @@
       </c>
       <c r="AJ329" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK329" t="inlineStr">
@@ -65648,7 +65648,7 @@
       </c>
       <c r="AJ331" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK331" t="inlineStr">
@@ -66830,7 +66830,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -67226,7 +67226,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -68408,7 +68408,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -68804,7 +68804,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -69986,7 +69986,7 @@
       </c>
       <c r="AJ353" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK353" t="inlineStr">
@@ -70382,7 +70382,7 @@
       </c>
       <c r="AJ355" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK355" t="inlineStr">
@@ -71564,7 +71564,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">
@@ -71960,7 +71960,7 @@
       </c>
       <c r="AJ363" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK363" t="inlineStr">
@@ -73142,7 +73142,7 @@
       </c>
       <c r="AJ369" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK369" t="inlineStr">
@@ -73538,7 +73538,7 @@
       </c>
       <c r="AJ371" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK371" t="inlineStr">
@@ -74720,7 +74720,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">
@@ -75116,7 +75116,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -76298,7 +76298,7 @@
       </c>
       <c r="AJ385" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK385" t="inlineStr">
@@ -76694,7 +76694,7 @@
       </c>
       <c r="AJ387" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK387" t="inlineStr">
@@ -77876,7 +77876,7 @@
       </c>
       <c r="AJ393" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK393" t="inlineStr">
@@ -78272,7 +78272,7 @@
       </c>
       <c r="AJ395" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK395" t="inlineStr">
@@ -79454,7 +79454,7 @@
       </c>
       <c r="AJ401" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK401" t="inlineStr">
@@ -79850,7 +79850,7 @@
       </c>
       <c r="AJ403" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK403" t="inlineStr">
@@ -81032,7 +81032,7 @@
       </c>
       <c r="AJ409" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK409" t="inlineStr">

--- a/diseases/d068/2000-2004.xlsx
+++ b/diseases/d068/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10460,7 +10460,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11642,7 +11642,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14006,7 +14006,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15188,7 +15188,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16370,7 +16370,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17552,7 +17552,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18734,7 +18734,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19916,7 +19916,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21098,7 +21098,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22280,7 +22280,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23462,7 +23462,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24644,7 +24644,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25826,7 +25826,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27008,7 +27008,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -28190,7 +28190,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29372,7 +29372,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31736,7 +31736,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32918,7 +32918,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -34100,7 +34100,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35282,7 +35282,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36464,7 +36464,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37646,7 +37646,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -38828,7 +38828,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -40010,7 +40010,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -41192,7 +41192,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42374,7 +42374,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -43556,7 +43556,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44738,7 +44738,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -45134,7 +45134,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46316,7 +46316,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -46712,7 +46712,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -47894,7 +47894,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -48290,7 +48290,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -49472,7 +49472,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -49868,7 +49868,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -51050,7 +51050,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -51446,7 +51446,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -52628,7 +52628,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -53024,7 +53024,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -54206,7 +54206,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -54602,7 +54602,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -55784,7 +55784,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -56180,7 +56180,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -57362,7 +57362,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -57758,7 +57758,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -58940,7 +58940,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -59336,7 +59336,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -60518,7 +60518,7 @@
       </c>
       <c r="AJ305" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK305" t="inlineStr">
@@ -60914,7 +60914,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -62096,7 +62096,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -62492,7 +62492,7 @@
       </c>
       <c r="AJ315" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK315" t="inlineStr">
@@ -63674,7 +63674,7 @@
       </c>
       <c r="AJ321" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK321" t="inlineStr">
@@ -64070,7 +64070,7 @@
       </c>
       <c r="AJ323" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK323" t="inlineStr">
@@ -65252,7 +65252,7 @@
       </c>
       <c r="AJ329" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK329" t="inlineStr">
@@ -65648,7 +65648,7 @@
       </c>
       <c r="AJ331" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK331" t="inlineStr">
@@ -66830,7 +66830,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -67226,7 +67226,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -68408,7 +68408,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -68804,7 +68804,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -69986,7 +69986,7 @@
       </c>
       <c r="AJ353" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK353" t="inlineStr">
@@ -70382,7 +70382,7 @@
       </c>
       <c r="AJ355" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK355" t="inlineStr">
@@ -71564,7 +71564,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">
@@ -71960,7 +71960,7 @@
       </c>
       <c r="AJ363" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK363" t="inlineStr">
@@ -73142,7 +73142,7 @@
       </c>
       <c r="AJ369" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK369" t="inlineStr">
@@ -73538,7 +73538,7 @@
       </c>
       <c r="AJ371" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK371" t="inlineStr">
@@ -74720,7 +74720,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">
@@ -75116,7 +75116,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -76298,7 +76298,7 @@
       </c>
       <c r="AJ385" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK385" t="inlineStr">
@@ -76694,7 +76694,7 @@
       </c>
       <c r="AJ387" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK387" t="inlineStr">
@@ -77876,7 +77876,7 @@
       </c>
       <c r="AJ393" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK393" t="inlineStr">
@@ -78272,7 +78272,7 @@
       </c>
       <c r="AJ395" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK395" t="inlineStr">
@@ -79454,7 +79454,7 @@
       </c>
       <c r="AJ401" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK401" t="inlineStr">
@@ -79850,7 +79850,7 @@
       </c>
       <c r="AJ403" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK403" t="inlineStr">
@@ -81032,7 +81032,7 @@
       </c>
       <c r="AJ409" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK409" t="inlineStr">
